--- a/site/Entra-ID-Group-Management-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Group-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,622 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01KRNED3NNWZXEVJF1F56K4214</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3NNWZXEVJF1F56K4214</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KRNED3NRCR7P5EHXW3XPKPC9</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3NRCR7P5EHXW3XPKPC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01KRNED3NVE3JDDJEW0E88H4YF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3NVE3JDDJEW0E88H4YF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01KRNED3NZ4H3A3BH65YZSAVBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3NZ4H3A3BH65YZSAVBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P06JCR58HZBR231VG6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P06JCR58HZBR231VG6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P4ZPD6RBJMQG7025C1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P4ZPD6RBJMQG7025C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Integration Overview</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P5ZTZQ7RZPBJ62M3ZX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P5ZTZQ7RZPBJ62M3ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DDL Feature Controls</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P5A1GE9RB05PH9C0AS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P5A1GE9RB05PH9C0AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Operational Features</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P6P7M00QR3CXQC4W97</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P6P7M00QR3CXQC4W97</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Group Management</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KRNED3P99HCYP9NS3KYHC7Q1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3P99HCYP9NS3KYHC7Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PAXNNVR9D81FVRWH39</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PAXNNVR9D81FVRWH39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DDL Management</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PAZ4A59G4R28VT55ZJ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PAZ4A59G4R28VT55ZJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Attribute Mapper</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PJ7K76V4JM243FP6FW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PJ7K76V4JM243FP6FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DDL Creation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PKZF4M07179DN3XST3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PKZF4M07179DN3XST3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Operation Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PPT9H2WJM7E1CVQKJ2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PPT9H2WJM7E1CVQKJ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PQ6P9ZEMRBWQX2163C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PQ6P9ZEMRBWQX2163C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PVRCNEFWBVTR2SW5HM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PVRCNEFWBVTR2SW5HM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KRNED3PYQJXM5P7Z2GPMGPNJ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3PYQJXM5P7Z2GPMGPNJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Advance Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q0D706ZB0JBW1S06Y8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q0D706ZB0JBW1S06Y8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q3ZJFV8MNWSW4ES7RX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q3ZJFV8MNWSW4ES7RX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q39B14ZHS2ABMACWDN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q39B14ZHS2ABMACWDN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Execution Success Notification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q5V31MTAEMWNAY6ZQB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q5V31MTAEMWNAY6ZQB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Execution Failure Notification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q7D71FM6HX56R5F244</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q7D71FM6HX56R5F244</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q97WQT14FWWTQJ0G8Y</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q97WQT14FWWTQJ0G8Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KRNED3Q9M0Q67MD3DNQJF495</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3Q9M0Q67MD3DNQJF495</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KRNED3QASH8FK0XF0DZ73WEN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3QASH8FK0XF0DZ73WEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Report Only Mode Behavior</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KRNED3QCGXKN3NJH274GERHD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3QCGXKN3NJH274GERHD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KRNED3QDVBB1VWTGXBGGJWA2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Group-Management-Integration-Guide/#h_01KRNED3QDVBB1VWTGXBGGJWA2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
